--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Signature.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Signature.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="234">
   <si>
     <t>Property</t>
   </si>
@@ -367,6 +367,9 @@
     <t>closed</t>
   </si>
   <si>
+    <t>CV</t>
+  </si>
+  <si>
     <t>Signature.type:AuthorsSignature</t>
   </si>
   <si>
@@ -483,6 +486,9 @@
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
@@ -577,6 +583,13 @@
   </si>
   <si>
     <t>A reference to an application-usable description of the identity that signed  (e.g. the signature used their private key).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Signature.who.id</t>
@@ -1087,7 +1100,7 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="60.26953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1610,24 +1623,24 @@
         <v>76</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>102</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>74</v>
@@ -1684,13 +1697,13 @@
         <v>74</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y6" t="s" s="2">
         <v>109</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>74</v>
@@ -1717,21 +1730,21 @@
         <v>76</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1831,10 +1844,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1936,10 +1949,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1962,26 +1975,26 @@
         <v>103</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -2023,7 +2036,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -2038,15 +2051,15 @@
         <v>82</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2072,13 +2085,13 @@
         <v>86</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2128,7 +2141,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2143,15 +2156,15 @@
         <v>82</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2174,24 +2187,24 @@
         <v>103</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S11" t="s" s="2">
         <v>74</v>
@@ -2233,7 +2246,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2248,15 +2261,15 @@
         <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2282,14 +2295,16 @@
         <v>86</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>74</v>
@@ -2338,7 +2353,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2353,15 +2368,15 @@
         <v>82</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2384,19 +2399,19 @@
         <v>103</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>74</v>
@@ -2445,7 +2460,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2460,18 +2475,18 @@
         <v>82</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>102</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>74</v>
@@ -2528,13 +2543,13 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y14" t="s" s="2">
         <v>109</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -2561,21 +2576,21 @@
         <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2675,10 +2690,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2780,10 +2795,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2806,26 +2821,26 @@
         <v>103</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>74</v>
@@ -2867,7 +2882,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2882,15 +2897,15 @@
         <v>82</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2916,13 +2931,13 @@
         <v>86</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2972,7 +2987,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2987,15 +3002,15 @@
         <v>82</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3018,24 +3033,24 @@
         <v>103</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>74</v>
@@ -3077,7 +3092,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3092,15 +3107,15 @@
         <v>82</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3126,14 +3141,16 @@
         <v>86</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N20" s="2"/>
+        <v>151</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="O20" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>74</v>
@@ -3182,7 +3199,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3197,15 +3214,15 @@
         <v>82</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3228,19 +3245,19 @@
         <v>103</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>74</v>
@@ -3289,7 +3306,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3304,15 +3321,15 @@
         <v>82</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3335,16 +3352,16 @@
         <v>103</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3394,7 +3411,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>85</v>
@@ -3414,10 +3431,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3440,16 +3457,16 @@
         <v>103</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -3499,7 +3516,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>85</v>
@@ -3508,21 +3525,21 @@
         <v>85</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>74</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3622,10 +3639,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3727,10 +3744,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3756,13 +3773,13 @@
         <v>86</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3812,7 +3829,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3821,7 +3838,7 @@
         <v>85</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>82</v>
@@ -3832,10 +3849,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3858,16 +3875,16 @@
         <v>103</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3893,13 +3910,13 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3917,7 +3934,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -3937,10 +3954,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3963,16 +3980,16 @@
         <v>103</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4022,7 +4039,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4031,21 +4048,21 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4071,13 +4088,13 @@
         <v>86</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4127,7 +4144,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4147,10 +4164,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4173,19 +4190,19 @@
         <v>103</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>74</v>
@@ -4234,7 +4251,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4243,21 +4260,21 @@
         <v>85</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>74</v>
+        <v>185</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4280,16 +4297,16 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4318,28 +4335,28 @@
         <v>108</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4359,10 +4376,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4385,13 +4402,13 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4421,10 +4438,10 @@
         <v>108</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4442,7 +4459,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4462,10 +4479,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4488,16 +4505,16 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4547,7 +4564,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>

--- a/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Signature.xlsx
+++ b/tiflow/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERP-PR-Signature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
